--- a/2026英仔爱心社报名表 的副本.xlsx
+++ b/2026英仔爱心社报名表 的副本.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\45120\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\yingzai-recruit\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{60E64E85-EAAF-42DB-BDB8-5BF025C52A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="28800" windowHeight="17145" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
